--- a/2VAR_ATSBR_T2W/2var_atsbr_t2w_PUBLICTR.xlsx
+++ b/2VAR_ATSBR_T2W/2var_atsbr_t2w_PUBLICTR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philliao/Downloads/Code/IB-Math-IA/2VAR_ATSBR_T2W/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE9ECEE-16FE-704A-9296-F4EF1D03B360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB4EAC4-281E-0B48-9CC2-C6BECD2317D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="660" windowWidth="21760" windowHeight="14320" xr2:uid="{50320A5D-4098-5A43-9B91-D26FAF5C6D92}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="25600" windowHeight="16000" xr2:uid="{50320A5D-4098-5A43-9B91-D26FAF5C6D92}"/>
   </bookViews>
   <sheets>
     <sheet name="Regression" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="33">
   <si>
     <t>district_name</t>
   </si>
@@ -56,12 +56,93 @@
   <si>
     <t>r value</t>
   </si>
+  <si>
+    <t>SUMMARY OUTPUT</t>
+  </si>
+  <si>
+    <t>Regression Statistics</t>
+  </si>
+  <si>
+    <t>Multiple R</t>
+  </si>
+  <si>
+    <t>R Square</t>
+  </si>
+  <si>
+    <t>Adjusted R Square</t>
+  </si>
+  <si>
+    <t>Standard Error</t>
+  </si>
+  <si>
+    <t>Observations</t>
+  </si>
+  <si>
+    <t>ANOVA</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>Residual</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Significance F</t>
+  </si>
+  <si>
+    <t>Coefficients</t>
+  </si>
+  <si>
+    <t>t Stat</t>
+  </si>
+  <si>
+    <t>P-value</t>
+  </si>
+  <si>
+    <t>Lower 95%</t>
+  </si>
+  <si>
+    <t>Upper 95%</t>
+  </si>
+  <si>
+    <t>Lower 95.0%</t>
+  </si>
+  <si>
+    <t>Upper 95.0%</t>
+  </si>
+  <si>
+    <t>speed_acr_rank</t>
+  </si>
+  <si>
+    <t>PUBLICTR_percent_rank</t>
+  </si>
+  <si>
+    <t>rho=</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -76,6 +157,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -85,7 +181,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -93,16 +189,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -152,11 +279,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Congestion</a:t>
+              <a:t>ATSBR</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t> rate to public transportation usage</a:t>
+              <a:t> PUBLICTR</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -238,8 +365,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-5.0849522188104866E-2"/>
-                  <c:y val="0.16791601049868765"/>
+                  <c:x val="-4.9615217016791821E-2"/>
+                  <c:y val="0.4304878390201225"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -612,6 +739,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -619,7 +747,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -689,11 +816,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Congestion</a:t>
+              <a:t>ATSBR PUBLICTR</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t> rate to public transportation usage (populated)</a:t>
+              <a:t> (Crowded)</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -775,8 +902,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-9.1951884392829281E-2"/>
-                  <c:y val="9.7132108486439189E-2"/>
+                  <c:x val="-6.7731736235673246E-2"/>
+                  <c:y val="0.27071111111111112"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -811,1021 +938,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Regression!$C$18:$C$29</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="6">
-                  <c:v>4.7154689999999997</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2.4929640000000002</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Regression!$B$18:$B$29</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="6">
-                  <c:v>5.5768249999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.5304152000000002E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FC22-464A-84EE-FC36E5978166}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1022506720"/>
-        <c:axId val="1022524240"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1022506720"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Public Transportation Usage (%)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1022524240"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1022524240"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Congestion Rate</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1022506720"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Congestion</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> rate to public transportation usage (unpopulated)</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-9.1790147853139978E-2"/>
-                  <c:y val="0.38769553805774276"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Regression!$C$34:$C$45</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>2.1459359999999998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.74672099999999997</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.266483</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.1496979999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.3315170000000001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.595407</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.3538140000000001</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>3.1974629999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Regression!$B$34:$B$45</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>-8.9864090000000008E-3</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-7.0764041999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.9098905999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-1.361688E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>8.6388139999999999E-3</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.9324102999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-7.7793280000000003E-3</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>3.3507642999999997E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-48D2-674C-9DB9-B4324ACD5E0F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1022506720"/>
-        <c:axId val="1022524240"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1022506720"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Public Transportation Usage (%)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1022524240"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1022524240"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Congestion Rate</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1022506720"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Congestion</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> rate to public transportation usage (crowded)</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-8.1025344804872362E-2"/>
-                  <c:y val="0.17935258092738407"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Regression!$C$50:$C$61</c:f>
+              <c:f>Regression!$R$2:$R$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1849,7 +962,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Regression!$B$50:$B$61</c:f>
+              <c:f>Regression!$Q$2:$Q$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -2133,6 +1246,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2140,7 +1254,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2175,7 +1288,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2209,12 +1322,8 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Congestion</a:t>
-            </a:r>
-            <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t> rate to public transportation usage (uncrowded)</a:t>
+              <a:t>ATSBR PUBLICTR (Uncrowded)</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2332,7 +1441,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Regression!$C$66:$C$77</c:f>
+              <c:f>Regression!$AG$2:$AG$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -2356,7 +1465,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Regression!$B$66:$B$77</c:f>
+              <c:f>Regression!$AF$2:$AF$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -2640,6 +1749,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2647,7 +1757,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2802,86 +1911,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3915,1038 +2944,6 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5502,23 +3499,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>806450</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="6" name="Chart 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13B21D92-4899-574D-AFA5-3B6E05EEE0C4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{319D13E3-86D8-CD44-AE80-E2A23743A664}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5540,91 +3537,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>35</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
+      <xdr:col>40</xdr:col>
       <xdr:colOff>806450</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18F9071B-922B-AD40-9FE6-E9ED4806ED7B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>806450</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{319D13E3-86D8-CD44-AE80-E2A23743A664}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>806450</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5646,7 +3567,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5972,10 +3893,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F4DD1BC-0C17-1B4E-8BBE-938092E54FB2}">
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:AR49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5985,8 +3906,26 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="P1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5996,8 +3935,20 @@
       <c r="C2">
         <v>2.1459359999999998</v>
       </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>-8.9864090000000008E-3</v>
+      </c>
+      <c r="AG2">
+        <v>2.1459359999999998</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6007,8 +3958,20 @@
       <c r="C3">
         <v>0.74672099999999997</v>
       </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="AE3">
+        <v>2</v>
+      </c>
+      <c r="AF3">
+        <v>-7.0764041999999999E-2</v>
+      </c>
+      <c r="AG3">
+        <v>0.74672099999999997</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6025,16 +3988,54 @@
         <f>CORREL(C2:C13,B2:B13)</f>
         <v>0.66344428426764801</v>
       </c>
+      <c r="P4">
+        <v>3</v>
+      </c>
+      <c r="Q4">
+        <v>1.9098905999999999E-2</v>
+      </c>
+      <c r="R4">
+        <v>2.266483</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB4">
+        <f>CORREL(R2:R13,Q2:Q13)</f>
+        <v>0.6909447202071346</v>
+      </c>
+      <c r="AE4">
+        <v>3</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ4">
+        <f>CORREL(AG2:AG13,AF2:AF13)</f>
+        <v>0.41970175235053775</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
       </c>
+      <c r="P5">
+        <v>4</v>
+      </c>
+      <c r="S5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE5">
+        <v>4</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6044,8 +4045,20 @@
       <c r="C6">
         <v>3.1496979999999999</v>
       </c>
+      <c r="P6">
+        <v>5</v>
+      </c>
+      <c r="AE6">
+        <v>5</v>
+      </c>
+      <c r="AF6">
+        <v>-1.361688E-2</v>
+      </c>
+      <c r="AG6">
+        <v>3.1496979999999999</v>
+      </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6055,8 +4068,20 @@
       <c r="C7">
         <v>1.3315170000000001</v>
       </c>
+      <c r="P7">
+        <v>6</v>
+      </c>
+      <c r="AE7">
+        <v>6</v>
+      </c>
+      <c r="AF7">
+        <v>8.6388139999999999E-3</v>
+      </c>
+      <c r="AG7">
+        <v>1.3315170000000001</v>
+      </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6066,8 +4091,20 @@
       <c r="C8">
         <v>4.7154689999999997</v>
       </c>
+      <c r="P8">
+        <v>7</v>
+      </c>
+      <c r="Q8">
+        <v>5.5768249999999998E-2</v>
+      </c>
+      <c r="R8">
+        <v>4.7154689999999997</v>
+      </c>
+      <c r="AE8">
+        <v>7</v>
+      </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6077,16 +4114,40 @@
       <c r="C9">
         <v>1.595407</v>
       </c>
+      <c r="P9">
+        <v>8</v>
+      </c>
+      <c r="Q9">
+        <v>1.9324102999999999E-2</v>
+      </c>
+      <c r="R9">
+        <v>1.595407</v>
+      </c>
+      <c r="AE9">
+        <v>8</v>
+      </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="D10" t="s">
         <v>4</v>
       </c>
+      <c r="P10">
+        <v>9</v>
+      </c>
+      <c r="S10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE10">
+        <v>9</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6096,8 +4157,20 @@
       <c r="C11">
         <v>1.3538140000000001</v>
       </c>
+      <c r="P11">
+        <v>10</v>
+      </c>
+      <c r="AE11">
+        <v>10</v>
+      </c>
+      <c r="AF11">
+        <v>-7.7793280000000003E-3</v>
+      </c>
+      <c r="AG11">
+        <v>1.3538140000000001</v>
+      </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6107,8 +4180,20 @@
       <c r="C12">
         <v>3.1974629999999999</v>
       </c>
+      <c r="P12">
+        <v>11</v>
+      </c>
+      <c r="Q12">
+        <v>3.3507642999999997E-2</v>
+      </c>
+      <c r="R12">
+        <v>3.1974629999999999</v>
+      </c>
+      <c r="AE12">
+        <v>11</v>
+      </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6118,59 +4203,269 @@
       <c r="C13">
         <v>2.4929640000000002</v>
       </c>
+      <c r="P13">
+        <v>12</v>
+      </c>
+      <c r="Q13">
+        <v>5.5304152000000002E-2</v>
+      </c>
+      <c r="R13">
+        <v>2.4929640000000002</v>
+      </c>
+      <c r="AE13">
+        <v>12</v>
+      </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>0</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>1</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>2</v>
       </c>
+      <c r="F18" t="s">
+        <v>6</v>
+      </c>
+      <c r="P18" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>1</v>
+      </c>
+      <c r="R18" t="s">
+        <v>2</v>
+      </c>
+      <c r="U18" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18">
+    <row r="19" spans="1:41" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>1</v>
       </c>
+      <c r="B19">
+        <v>-8.9864090000000008E-3</v>
+      </c>
+      <c r="C19">
+        <v>2.1459359999999998</v>
+      </c>
+      <c r="P19">
+        <v>3</v>
+      </c>
+      <c r="Q19">
+        <v>1.9098905999999999E-2</v>
+      </c>
+      <c r="R19">
+        <v>2.266483</v>
+      </c>
+      <c r="AE19">
+        <v>1</v>
+      </c>
+      <c r="AF19">
+        <v>-8.9864090000000008E-3</v>
+      </c>
+      <c r="AG19">
+        <v>2.1459359999999998</v>
+      </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A20">
         <v>2</v>
       </c>
+      <c r="B20">
+        <v>-7.0764041999999999E-2</v>
+      </c>
+      <c r="C20">
+        <v>0.74672099999999997</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="P20">
+        <v>7</v>
+      </c>
+      <c r="Q20">
+        <v>5.5768249999999998E-2</v>
+      </c>
+      <c r="R20">
+        <v>4.7154689999999997</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="V20" s="4"/>
+      <c r="AE20">
+        <v>2</v>
+      </c>
+      <c r="AF20">
+        <v>-7.0764041999999999E-2</v>
+      </c>
+      <c r="AG20">
+        <v>0.74672099999999997</v>
+      </c>
+      <c r="AJ20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK20" s="4"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A21">
         <v>3</v>
       </c>
-      <c r="L20" t="s">
+      <c r="B21">
+        <v>1.9098905999999999E-2</v>
+      </c>
+      <c r="C21">
+        <v>2.266483</v>
+      </c>
+      <c r="F21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21">
+        <v>0.6634442842676479</v>
+      </c>
+      <c r="P21">
+        <v>8</v>
+      </c>
+      <c r="Q21">
+        <v>1.9324102999999999E-2</v>
+      </c>
+      <c r="R21">
+        <v>1.595407</v>
+      </c>
+      <c r="U21" t="s">
+        <v>8</v>
+      </c>
+      <c r="V21">
+        <v>0.69094472020713471</v>
+      </c>
+      <c r="AE21">
         <v>5</v>
       </c>
-      <c r="M20">
-        <f>CORREL(C18:C29,B18:B29)</f>
-        <v>1</v>
+      <c r="AF21">
+        <v>-1.361688E-2</v>
+      </c>
+      <c r="AG21">
+        <v>3.1496979999999999</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK21">
+        <v>0.41970175235053792</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>4</v>
-      </c>
-      <c r="D21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>5</v>
       </c>
+      <c r="B22">
+        <v>-1.361688E-2</v>
+      </c>
+      <c r="C22">
+        <v>3.1496979999999999</v>
+      </c>
+      <c r="F22" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22">
+        <v>0.44015831832741154</v>
+      </c>
+      <c r="P22">
+        <v>11</v>
+      </c>
+      <c r="Q22">
+        <v>3.3507642999999997E-2</v>
+      </c>
+      <c r="R22">
+        <v>3.1974629999999999</v>
+      </c>
+      <c r="U22" t="s">
+        <v>9</v>
+      </c>
+      <c r="V22">
+        <v>0.47740460638211568</v>
+      </c>
+      <c r="AE22">
+        <v>6</v>
+      </c>
+      <c r="AF22">
+        <v>8.6388139999999999E-3</v>
+      </c>
+      <c r="AG22">
+        <v>1.3315170000000001</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK22">
+        <v>0.17614956092611228</v>
+      </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>6</v>
       </c>
+      <c r="B23">
+        <v>8.6388139999999999E-3</v>
+      </c>
+      <c r="C23">
+        <v>1.3315170000000001</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>0.37017810811833796</v>
+      </c>
+      <c r="P23">
+        <v>12</v>
+      </c>
+      <c r="Q23">
+        <v>5.5304152000000002E-2</v>
+      </c>
+      <c r="R23">
+        <v>2.4929640000000002</v>
+      </c>
+      <c r="U23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V23">
+        <v>0.30320614184282091</v>
+      </c>
+      <c r="AE23">
+        <v>10</v>
+      </c>
+      <c r="AF23">
+        <v>-7.7793280000000003E-3</v>
+      </c>
+      <c r="AG23">
+        <v>1.3538140000000001</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK23">
+        <v>-9.8467252098516964E-2</v>
+      </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>7</v>
       </c>
@@ -6180,403 +4475,945 @@
       <c r="C24">
         <v>4.7154689999999997</v>
       </c>
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24">
+        <v>2.9717292529919673E-2</v>
+      </c>
+      <c r="U24" t="s">
+        <v>11</v>
+      </c>
+      <c r="V24">
+        <v>1.5230176169014347E-2</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK24">
+        <v>3.1864547083152187E-2</v>
+      </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:41" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>8</v>
       </c>
+      <c r="B25">
+        <v>1.9324102999999999E-2</v>
+      </c>
+      <c r="C25">
+        <v>1.595407</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="2">
+        <v>10</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="V25" s="2">
+        <v>5</v>
+      </c>
+      <c r="AJ25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AK25" s="2">
+        <v>5</v>
+      </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A26">
+        <v>10</v>
+      </c>
+      <c r="B26">
+        <v>-7.7793280000000003E-3</v>
+      </c>
+      <c r="C26">
+        <v>1.3538140000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:41" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>3.3507642999999997E-2</v>
+      </c>
+      <c r="C27">
+        <v>3.1974629999999999</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="U27" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>12</v>
+      </c>
+      <c r="B28">
+        <v>5.5304152000000002E-2</v>
+      </c>
+      <c r="C28">
+        <v>2.4929640000000002</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="X28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AJ28" s="3"/>
+      <c r="AK28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AN28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AO28" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>5.5545918146881973E-3</v>
+      </c>
+      <c r="I29">
+        <v>5.5545918146881973E-3</v>
+      </c>
+      <c r="J29">
+        <v>6.2897541606747138</v>
+      </c>
+      <c r="K29" s="5">
+        <v>3.6487943984376152E-2</v>
+      </c>
+      <c r="U29" t="s">
+        <v>14</v>
+      </c>
+      <c r="V29">
+        <v>1</v>
+      </c>
+      <c r="W29">
+        <v>6.3569988998547745E-4</v>
+      </c>
+      <c r="X29">
+        <v>6.3569988998547745E-4</v>
+      </c>
+      <c r="Y29">
+        <v>2.7405787280887615</v>
+      </c>
+      <c r="Z29" s="5">
+        <v>0.19640488223555827</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK29">
+        <v>1</v>
+      </c>
+      <c r="AL29">
+        <v>6.5128329953355281E-4</v>
+      </c>
+      <c r="AM29">
+        <v>6.5128329953355281E-4</v>
+      </c>
+      <c r="AN29">
+        <v>0.64143764173067641</v>
+      </c>
+      <c r="AO29" s="5">
+        <v>0.48175071777337292</v>
+      </c>
+    </row>
+    <row r="30" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="F30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30">
+        <v>8</v>
+      </c>
+      <c r="H30">
+        <v>7.0649398024705571E-3</v>
+      </c>
+      <c r="I30">
+        <v>8.8311747530881964E-4</v>
+      </c>
+      <c r="U30" t="s">
+        <v>15</v>
+      </c>
+      <c r="V30">
+        <v>3</v>
+      </c>
+      <c r="W30">
+        <v>6.9587479841763753E-4</v>
+      </c>
+      <c r="X30">
+        <v>2.3195826613921252E-4</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK30">
+        <v>3</v>
+      </c>
+      <c r="AL30">
+        <v>3.0460480824432675E-3</v>
+      </c>
+      <c r="AM30">
+        <v>1.0153493608144224E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:41" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" s="2">
         <v>9</v>
       </c>
-      <c r="D26" t="s">
+      <c r="H31" s="2">
+        <v>1.2619531617158754E-2</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="U31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="V31" s="2">
         <v>4</v>
       </c>
+      <c r="W31" s="2">
+        <v>1.331574688403115E-3</v>
+      </c>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
+      <c r="Z31" s="2"/>
+      <c r="AJ31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK31" s="2">
+        <v>4</v>
+      </c>
+      <c r="AL31" s="2">
+        <v>3.6973313819768203E-3</v>
+      </c>
+      <c r="AM31" s="2"/>
+      <c r="AN31" s="2"/>
+      <c r="AO31" s="2"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27">
+    <row r="32" spans="1:41" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="F33" s="3"/>
+      <c r="G33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ33" s="3"/>
+      <c r="AK33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AN33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AR33" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="F34" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34">
+        <v>-4.0085145424990351E-2</v>
+      </c>
+      <c r="H34">
+        <v>2.1728892826843243E-2</v>
+      </c>
+      <c r="I34">
+        <v>-1.8447854542993707</v>
+      </c>
+      <c r="J34" s="5">
+        <v>0.10229181884508708</v>
+      </c>
+      <c r="K34">
+        <v>-9.019206213709903E-2</v>
+      </c>
+      <c r="L34">
+        <v>1.0021771287118331E-2</v>
+      </c>
+      <c r="M34">
+        <v>-9.019206213709903E-2</v>
+      </c>
+      <c r="N34">
+        <v>1.0021771287118331E-2</v>
+      </c>
+      <c r="U34" t="s">
+        <v>17</v>
+      </c>
+      <c r="V34">
+        <v>6.312474779407818E-3</v>
+      </c>
+      <c r="W34">
+        <v>1.952249864485368E-2</v>
+      </c>
+      <c r="X34">
+        <v>0.32334358906829008</v>
+      </c>
+      <c r="Y34" s="5">
+        <v>0.76766322029123257</v>
+      </c>
+      <c r="Z34">
+        <v>-5.5816828902812997E-2</v>
+      </c>
+      <c r="AA34">
+        <v>6.8441778461628633E-2</v>
+      </c>
+      <c r="AB34">
+        <v>-5.5816828902812997E-2</v>
+      </c>
+      <c r="AC34">
+        <v>6.8441778461628633E-2</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK34">
+        <v>-4.2469067934808022E-2</v>
+      </c>
+      <c r="AL34">
+        <v>3.3145471030748032E-2</v>
+      </c>
+      <c r="AM34">
+        <v>-1.2812932389891452</v>
+      </c>
+      <c r="AN34" s="5">
+        <v>0.29015276948763075</v>
+      </c>
+      <c r="AO34">
+        <v>-0.14795274975350031</v>
+      </c>
+      <c r="AP34">
+        <v>6.3014613883884268E-2</v>
+      </c>
+      <c r="AQ34">
+        <v>-0.14795274975350031</v>
+      </c>
+      <c r="AR34">
+        <v>6.3014613883884268E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F35" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="2">
+        <v>2.1367104934828192E-2</v>
+      </c>
+      <c r="H35" s="2">
+        <v>8.5197891588488818E-3</v>
+      </c>
+      <c r="I35" s="2">
+        <v>2.507938229038889</v>
+      </c>
+      <c r="J35" s="6">
+        <v>3.6487943984376082E-2</v>
+      </c>
+      <c r="K35" s="2">
+        <v>1.7204359034550378E-3</v>
+      </c>
+      <c r="L35" s="2">
+        <v>4.1013773966201345E-2</v>
+      </c>
+      <c r="M35" s="2">
+        <v>1.7204359034550378E-3</v>
+      </c>
+      <c r="N35" s="2">
+        <v>4.1013773966201345E-2</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="V35" s="2">
+        <v>1.061416817598476E-2</v>
+      </c>
+      <c r="W35" s="2">
+        <v>6.4115764238105027E-3</v>
+      </c>
+      <c r="X35" s="2">
+        <v>1.6554693377072138</v>
+      </c>
+      <c r="Y35" s="6">
+        <v>0.19640488223555827</v>
+      </c>
+      <c r="Z35" s="2">
+        <v>-9.7903295250151116E-3</v>
+      </c>
+      <c r="AA35" s="2">
+        <v>3.1018665876984632E-2</v>
+      </c>
+      <c r="AB35" s="2">
+        <v>-9.7903295250151116E-3</v>
+      </c>
+      <c r="AC35" s="2">
+        <v>3.1018665876984632E-2</v>
+      </c>
+      <c r="AJ35" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK35" s="2">
+        <v>1.3730729390819067E-2</v>
+      </c>
+      <c r="AL35" s="2">
+        <v>1.7144166938504627E-2</v>
+      </c>
+      <c r="AM35" s="2">
+        <v>0.80089802205441596</v>
+      </c>
+      <c r="AN35" s="6">
+        <v>0.48175071777337347</v>
+      </c>
+      <c r="AO35" s="2">
+        <v>-4.08296613397921E-2</v>
+      </c>
+      <c r="AP35" s="2">
+        <v>6.8291120121430238E-2</v>
+      </c>
+      <c r="AQ35" s="2">
+        <v>-4.08296613397921E-2</v>
+      </c>
+      <c r="AR35" s="2">
+        <v>6.8291120121430238E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" t="s">
+        <v>2</v>
+      </c>
+      <c r="P39" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>1</v>
+      </c>
+      <c r="R39" t="s">
+        <v>30</v>
+      </c>
+      <c r="S39" t="s">
+        <v>2</v>
+      </c>
+      <c r="T39" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE39" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>1</v>
+      </c>
+      <c r="B40">
+        <v>-8.9864090000000008E-3</v>
+      </c>
+      <c r="C40">
+        <f>_xlfn.RANK.AVG(B40, B$40:B$49, 1)</f>
+        <v>3</v>
+      </c>
+      <c r="D40">
+        <v>2.1459359999999998</v>
+      </c>
+      <c r="E40">
+        <f>_xlfn.RANK.AVG(D40, D$40:D$49, 1)</f>
+        <v>5</v>
+      </c>
+      <c r="G40" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40">
+        <f>CORREL(C40:C49, E40:E49)</f>
+        <v>0.61212121212121207</v>
+      </c>
+      <c r="P40">
+        <v>3</v>
+      </c>
+      <c r="Q40">
+        <v>1.9098905999999999E-2</v>
+      </c>
+      <c r="R40">
+        <f>_xlfn.RANK.AVG(Q40, Q$40:Q$44,1)</f>
+        <v>1</v>
+      </c>
+      <c r="S40">
+        <v>2.266483</v>
+      </c>
+      <c r="T40">
+        <f>_xlfn.RANK.AVG(S40, S$40:S$44,1)</f>
+        <v>2</v>
+      </c>
+      <c r="V40" t="s">
+        <v>32</v>
+      </c>
+      <c r="W40">
+        <f>CORREL(R40:R44, T40:T44)</f>
+        <v>0.79999999999999982</v>
+      </c>
+      <c r="AE40">
+        <v>1</v>
+      </c>
+      <c r="AF40">
+        <v>-8.9864090000000008E-3</v>
+      </c>
+      <c r="AG40">
+        <f>_xlfn.RANK.AVG(AF40, AF$40:AF$44,1)</f>
+        <v>3</v>
+      </c>
+      <c r="AH40">
+        <v>2.1459359999999998</v>
+      </c>
+      <c r="AI40">
+        <f>_xlfn.RANK.AVG(AH40, AH$40:AH$44,1)</f>
+        <v>4</v>
+      </c>
+      <c r="AK40" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL40">
+        <f>CORREL(AG40:AG44, AI40:AI44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>2</v>
+      </c>
+      <c r="B41">
+        <v>-7.0764041999999999E-2</v>
+      </c>
+      <c r="C41">
+        <f t="shared" ref="C41:C49" si="0">_xlfn.RANK.AVG(B41, B$40:B$49, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>0.74672099999999997</v>
+      </c>
+      <c r="E41">
+        <f t="shared" ref="E41:E49" si="1">_xlfn.RANK.AVG(D41, D$40:D$49, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="P41">
+        <v>7</v>
+      </c>
+      <c r="Q41">
+        <v>5.5768249999999998E-2</v>
+      </c>
+      <c r="R41">
+        <f t="shared" ref="R41:R44" si="2">_xlfn.RANK.AVG(Q41, Q$40:Q$44,1)</f>
+        <v>5</v>
+      </c>
+      <c r="S41">
+        <v>4.7154689999999997</v>
+      </c>
+      <c r="T41">
+        <f t="shared" ref="T41:T44" si="3">_xlfn.RANK.AVG(S41, S$40:S$44,1)</f>
+        <v>5</v>
+      </c>
+      <c r="AE41">
+        <v>2</v>
+      </c>
+      <c r="AF41">
+        <v>-7.0764041999999999E-2</v>
+      </c>
+      <c r="AG41">
+        <f t="shared" ref="AG41:AG44" si="4">_xlfn.RANK.AVG(AF41, AF$40:AF$44,1)</f>
+        <v>1</v>
+      </c>
+      <c r="AH41">
+        <v>0.74672099999999997</v>
+      </c>
+      <c r="AI41">
+        <f t="shared" ref="AI41:AI44" si="5">_xlfn.RANK.AVG(AH41, AH$40:AH$44,1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42">
+        <v>1.9098905999999999E-2</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D42">
+        <v>2.266483</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="P42">
+        <v>8</v>
+      </c>
+      <c r="Q42">
+        <v>1.9324102999999999E-2</v>
+      </c>
+      <c r="R42">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="S42">
+        <v>1.595407</v>
+      </c>
+      <c r="T42">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AE42">
+        <v>5</v>
+      </c>
+      <c r="AF42">
+        <v>-1.361688E-2</v>
+      </c>
+      <c r="AG42">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH42">
+        <v>3.1496979999999999</v>
+      </c>
+      <c r="AI42">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>5</v>
+      </c>
+      <c r="B43">
+        <v>-1.361688E-2</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D43">
+        <v>3.1496979999999999</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="P43">
+        <v>11</v>
+      </c>
+      <c r="Q43">
+        <v>3.3507642999999997E-2</v>
+      </c>
+      <c r="R43">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="S43">
+        <v>3.1974629999999999</v>
+      </c>
+      <c r="T43">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AE43">
+        <v>6</v>
+      </c>
+      <c r="AF43">
+        <v>8.6388139999999999E-3</v>
+      </c>
+      <c r="AG43">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AH43">
+        <v>1.3315170000000001</v>
+      </c>
+      <c r="AI43">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>6</v>
+      </c>
+      <c r="B44">
+        <v>8.6388139999999999E-3</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D44">
+        <v>1.3315170000000001</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="P44">
+        <v>12</v>
+      </c>
+      <c r="Q44">
+        <v>5.5304152000000002E-2</v>
+      </c>
+      <c r="R44">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="S44">
+        <v>2.4929640000000002</v>
+      </c>
+      <c r="T44">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="AE44">
         <v>10</v>
       </c>
+      <c r="AF44">
+        <v>-7.7793280000000003E-3</v>
+      </c>
+      <c r="AG44">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH44">
+        <v>1.3538140000000001</v>
+      </c>
+      <c r="AI44">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28">
+    <row r="45" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>7</v>
+      </c>
+      <c r="B45">
+        <v>5.5768249999999998E-2</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="D45">
+        <v>4.7154689999999997</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>8</v>
+      </c>
+      <c r="B46">
+        <v>1.9324102999999999E-2</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="D46">
+        <v>1.595407</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>10</v>
+      </c>
+      <c r="B47">
+        <v>-7.7793280000000003E-3</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D47">
+        <v>1.3538140000000001</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A48">
         <v>11</v>
       </c>
+      <c r="B48">
+        <v>3.3507642999999997E-2</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D48">
+        <v>3.1974629999999999</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49">
         <v>12</v>
       </c>
-      <c r="B29">
+      <c r="B49">
         <v>5.5304152000000002E-2</v>
       </c>
-      <c r="C29">
+      <c r="C49">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="D49">
         <v>2.4929640000000002</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>1</v>
-      </c>
-      <c r="B34">
-        <v>-8.9864090000000008E-3</v>
-      </c>
-      <c r="C34">
-        <v>2.1459359999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>2</v>
-      </c>
-      <c r="B35">
-        <v>-7.0764041999999999E-2</v>
-      </c>
-      <c r="C35">
-        <v>0.74672099999999997</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>3</v>
-      </c>
-      <c r="B36">
-        <v>1.9098905999999999E-2</v>
-      </c>
-      <c r="C36">
-        <v>2.266483</v>
-      </c>
-      <c r="L36" t="s">
-        <v>5</v>
-      </c>
-      <c r="M36">
-        <f>CORREL(C34:C45,B34:B45)</f>
-        <v>0.54409720592532473</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>4</v>
-      </c>
-      <c r="D37" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>5</v>
-      </c>
-      <c r="B38">
-        <v>-1.361688E-2</v>
-      </c>
-      <c r="C38">
-        <v>3.1496979999999999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>6</v>
-      </c>
-      <c r="B39">
-        <v>8.6388139999999999E-3</v>
-      </c>
-      <c r="C39">
-        <v>1.3315170000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A40">
+      <c r="E49">
+        <f t="shared" si="1"/>
         <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>8</v>
-      </c>
-      <c r="B41">
-        <v>1.9324102999999999E-2</v>
-      </c>
-      <c r="C41">
-        <v>1.595407</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>9</v>
-      </c>
-      <c r="D42" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>10</v>
-      </c>
-      <c r="B43">
-        <v>-7.7793280000000003E-3</v>
-      </c>
-      <c r="C43">
-        <v>1.3538140000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>11</v>
-      </c>
-      <c r="B44">
-        <v>3.3507642999999997E-2</v>
-      </c>
-      <c r="C44">
-        <v>3.1974629999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>0</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1</v>
-      </c>
-      <c r="C49" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52">
-        <v>3</v>
-      </c>
-      <c r="B52">
-        <v>1.9098905999999999E-2</v>
-      </c>
-      <c r="C52">
-        <v>2.266483</v>
-      </c>
-      <c r="L52" t="s">
-        <v>5</v>
-      </c>
-      <c r="M52">
-        <f>CORREL(C50:C61,B50:B61)</f>
-        <v>0.6909447202071346</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="D53" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A54">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A55">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A56">
-        <v>7</v>
-      </c>
-      <c r="B56">
-        <v>5.5768249999999998E-2</v>
-      </c>
-      <c r="C56">
-        <v>4.7154689999999997</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57">
-        <v>8</v>
-      </c>
-      <c r="B57">
-        <v>1.9324102999999999E-2</v>
-      </c>
-      <c r="C57">
-        <v>1.595407</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58">
-        <v>9</v>
-      </c>
-      <c r="D58" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A59">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A60">
-        <v>11</v>
-      </c>
-      <c r="B60">
-        <v>3.3507642999999997E-2</v>
-      </c>
-      <c r="C60">
-        <v>3.1974629999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A61">
-        <v>12</v>
-      </c>
-      <c r="B61">
-        <v>5.5304152000000002E-2</v>
-      </c>
-      <c r="C61">
-        <v>2.4929640000000002</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>0</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1</v>
-      </c>
-      <c r="C65" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A66">
-        <v>1</v>
-      </c>
-      <c r="B66">
-        <v>-8.9864090000000008E-3</v>
-      </c>
-      <c r="C66">
-        <v>2.1459359999999998</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A67">
-        <v>2</v>
-      </c>
-      <c r="B67">
-        <v>-7.0764041999999999E-2</v>
-      </c>
-      <c r="C67">
-        <v>0.74672099999999997</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A68">
-        <v>3</v>
-      </c>
-      <c r="L68" t="s">
-        <v>5</v>
-      </c>
-      <c r="M68">
-        <f>CORREL(C66:C77,B66:B77)</f>
-        <v>0.41970175235053775</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A69">
-        <v>4</v>
-      </c>
-      <c r="D69" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A70">
-        <v>5</v>
-      </c>
-      <c r="B70">
-        <v>-1.361688E-2</v>
-      </c>
-      <c r="C70">
-        <v>3.1496979999999999</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A71">
-        <v>6</v>
-      </c>
-      <c r="B71">
-        <v>8.6388139999999999E-3</v>
-      </c>
-      <c r="C71">
-        <v>1.3315170000000001</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A72">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A73">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A74">
-        <v>9</v>
-      </c>
-      <c r="D74" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A75">
-        <v>10</v>
-      </c>
-      <c r="B75">
-        <v>-7.7793280000000003E-3</v>
-      </c>
-      <c r="C75">
-        <v>1.3538140000000001</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A76">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A77">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>

--- a/2VAR_ATSBR_T2W/2var_atsbr_t2w_PUBLICTR.xlsx
+++ b/2VAR_ATSBR_T2W/2var_atsbr_t2w_PUBLICTR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philliao/Downloads/Code/IB-Math-IA/2VAR_ATSBR_T2W/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB4EAC4-281E-0B48-9CC2-C6BECD2317D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CB39A1-BEB3-6E40-9DE0-46A530F0C79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="25600" windowHeight="16000" xr2:uid="{50320A5D-4098-5A43-9B91-D26FAF5C6D92}"/>
+    <workbookView xWindow="3840" yWindow="660" windowWidth="21760" windowHeight="14320" xr2:uid="{50320A5D-4098-5A43-9B91-D26FAF5C6D92}"/>
   </bookViews>
   <sheets>
     <sheet name="Regression" sheetId="1" r:id="rId1"/>
